--- a/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260812.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260812.xlsx
@@ -616,51 +616,51 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>16.92%</t>
+          <t>16.94%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>79,000,000</t>
+          <t>3,515,000</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>5.41%</t>
+          <t>5.66%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>3,450,000</t>
+          <t>79,000,000</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>5.31%</t>
+          <t>5.37%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>1,600,000</t>
+          <t>1,635,000</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>4.93%</t>
+          <t>5.18%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.48%</t>
+          <t>4.44%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>4.20%</t>
+          <t>4.14%</t>
         </is>
       </c>
     </row>
@@ -765,144 +765,144 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>1,050,000</t>
+          <t>1,060,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.69%</t>
+          <t>3.87%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>9,000,000</t>
+          <t>3,040,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.09%</t>
+          <t>3.01%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>3,040,000</t>
+          <t>9,000,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.06%</t>
+          <t>3.00%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>8,000,000</t>
+          <t>2,307,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.80%</t>
+          <t>2.83%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>2,307,000</t>
+          <t>8,000,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.74%</t>
+          <t>2.75%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>4,250,000</t>
+          <t>214,500</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>1.99%</t>
+          <t>2.06%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>199,500</t>
+          <t>4,250,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.83%</t>
+          <t>2.02%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>1.98%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.65%</t>
+          <t>1.67%</t>
         </is>
       </c>
     </row>
@@ -968,51 +968,51 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.50%</t>
+          <t>1.49%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>1,200,000</t>
+          <t>510,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>1.45%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>510,000</t>
+          <t>1,200,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.41%</t>
+          <t>1.43%</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>1.37%</t>
         </is>
       </c>
     </row>
@@ -1073,271 +1073,271 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>1,750,000</t>
+          <t>1,795,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.12%</t>
+          <t>1.26%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>897,000</t>
+          <t>462,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.04%</t>
+          <t>1.17%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>1,600,000</t>
+          <t>897,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>1.09%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>5,360,000</t>
+          <t>1,600,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>1.04%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>5,360,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>0.83%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>700,000</t>
+          <t>7,000,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.70%</t>
+          <t>0.73%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>6,000,000</t>
+          <t>700,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.64%</t>
+          <t>0.71%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>260,000</t>
+          <t>1,500,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>0.60%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>165,000</t>
+          <t>7,498,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>0.57%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>1,500,000</t>
+          <t>3,200,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>0.48%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>7,498,000</t>
+          <t>130,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.55%</t>
+          <t>0.47%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>順達</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>3,200,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>0.46%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>順達</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>1,600,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1349,34 +1349,34 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>1,600,000</t>
+          <t>900,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>0.37%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -1386,73 +1386,73 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.21%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>上銀</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>1,312,000</t>
+          <t>1,010,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>0.21%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2049</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>上銀</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>1,010,000</t>
+          <t>225,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>0.20%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>漢唐</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>225,000</t>
+          <t>250,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.18%</t>
+          <t>0.16%</t>
         </is>
       </c>
     </row>
@@ -1474,73 +1474,73 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.17%</t>
+          <t>0.16%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>漢唐</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>250,000</t>
+          <t>500,000</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.16%</t>
+          <t>0.13%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>1717</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>長興</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>1,100,000</t>
+          <t>2,500,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.09%</t>
+          <t>0.11%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>1717</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>長興</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>2,300,000</t>
+          <t>1,100,000</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.09%</t>
+          <t>0.08%</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.09%</t>
+          <t>0.08%</t>
         </is>
       </c>
     </row>
@@ -1623,24 +1623,24 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>200,000</t>
+          <t>150,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.05%</t>
+          <t>0.04%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -1657,12 +1657,12 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -1679,12 +1679,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>12,423,561,761</t>
+          <t>11,939,092,388</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr"/>
@@ -1747,7 +1747,7 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>-570,770,162</t>
+          <t>-832,613,484</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr"/>
